--- a/data/trans_bre/IP43-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP43-Edad-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 3,89</t>
+          <t>-9,76; 4,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 5,53</t>
+          <t>-8,66; 6,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-45,46; 21,9</t>
+          <t>-38,46; 25,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,52; 47,67</t>
+          <t>-43,33; 49,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 6,25</t>
+          <t>-6,14; 6,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 7,83</t>
+          <t>-1,79; 7,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 31,46</t>
+          <t>-23,76; 33,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 94,83</t>
+          <t>-15,33; 100,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 11,09</t>
+          <t>-5,49; 10,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 4,28</t>
+          <t>-5,53; 4,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 56,9</t>
+          <t>-19,92; 54,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-43,32; 63,84</t>
+          <t>-44,66; 56,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 5,56</t>
+          <t>-8,9; 6,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 7,17</t>
+          <t>-5,49; 6,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,41; 28,17</t>
+          <t>-32,57; 34,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,26; 74,01</t>
+          <t>-34,33; 70,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 2,81</t>
+          <t>-4,12; 3,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,6</t>
+          <t>-1,72; 3,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 13,21</t>
+          <t>-16,38; 13,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 35,85</t>
+          <t>-13,83; 35,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
